--- a/docentes/Torres Sánchez José Luis - Estadisticos 20231.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20231.xlsx
@@ -662,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -679,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20231.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20231.xlsx
@@ -662,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -688,7 +688,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20231.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20231.xlsx
@@ -662,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -688,7 +688,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
